--- a/asset/auto_gst database.xlsx
+++ b/asset/auto_gst database.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\D_TECH\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ganesh\ElitesecomTasks\asset\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2D754C3-9740-4240-896E-ECE669BE9C0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D8055B5-25EF-43E1-887F-A972B5943D84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="tables" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="174">
   <si>
     <t>email</t>
   </si>
@@ -1107,13 +1107,719 @@
   </si>
   <si>
     <t>2. DropShipRtvReports</t>
+  </si>
+  <si>
+    <t>worksheet</t>
+  </si>
+  <si>
+    <t>Seller Invoice No</t>
+  </si>
+  <si>
+    <t>Total Value</t>
+  </si>
+  <si>
+    <t>Total Price</t>
+  </si>
+  <si>
+    <t>Credit Note Number</t>
+  </si>
+  <si>
+    <t>Credit Note Generation Date</t>
+  </si>
+  <si>
+    <t>Credit Note Value</t>
+  </si>
+  <si>
+    <t>Credit Note Pre Tax Value</t>
+  </si>
+  <si>
+    <t>Limeroad</t>
+  </si>
+  <si>
+    <t>1. GSTR Report</t>
+  </si>
+  <si>
+    <t>tcs summary</t>
+  </si>
+  <si>
+    <t>Net Taxable Amount</t>
+  </si>
+  <si>
+    <t>Snapdeal</t>
+  </si>
+  <si>
+    <t>Aggregate Taxable Value</t>
+  </si>
+  <si>
+    <t>1. GSTR Return Report</t>
+  </si>
+  <si>
+    <t>Section 7(B)(2) in GSTR-1</t>
+  </si>
+  <si>
+    <t>formula</t>
+  </si>
+  <si>
+    <t>output file formula</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(gstr1 report file b2cs worksheet) taxable value (state wise)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (tcs_sales file) total_taxable_sale_value(state wise)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="16"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>-</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(tcs_sales_return file) total_taxable_sale_value(state wise)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(gstr1 report file b2b,sez,de worksheet) taxable value (invoice number wise)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Total Price (invoice number wise)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(gstr1 report file b2b,sez,de worksheet) invoice value (invoice number wise)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Total value (invoice number wise)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(gstr1 report file cdnr worksheet) note value (Credit Note Number wise)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Credit Note Value (Credit Note Number wise)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(gstr1 report file cdnr worksheet) taxable value (Credit Note Number wise)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Credit Note Pre Tax Value (Credit Note Number wise)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(gstr1 report file b2cs worksheet) taxable value (state wise)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(GSTR Return Report file worksheet Section 7(B)(2) in GSTR-1) Aggregate Taxable Value(state wise)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(gstr1 report file b2cs worksheet) taxable value (state wise)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(packed file) base_value(state wise)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">  </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="16"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>-</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (rto file) base_value(state wise)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="16"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>-</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">(rt file) base_value(state wise) </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(gstr1 report file b2cs worksheet) taxable value (state wise)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(sales report file Sales Report worksheet) Taxable Value (Final Invoice Amount -Taxes)(state wise)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(sales report file cash back Report worksheet)Taxable Value(state wise)</t>
+    </r>
+  </si>
+  <si>
+    <t>meesho_mp</t>
+  </si>
+  <si>
+    <t>tcs_sales_total_taxable_sale_value</t>
+  </si>
+  <si>
+    <t>tcs_sales_return_total_taxable_sale_value</t>
+  </si>
+  <si>
+    <t>myntra_mp</t>
+  </si>
+  <si>
+    <t>flipcart_mp</t>
+  </si>
+  <si>
+    <t>ajio_mp</t>
+  </si>
+  <si>
+    <t>limeroad_mp</t>
+  </si>
+  <si>
+    <t>snapdeal_mp</t>
+  </si>
+  <si>
+    <t>packed_base_value</t>
+  </si>
+  <si>
+    <t>rto_base_value</t>
+  </si>
+  <si>
+    <t>rt_base_value</t>
+  </si>
+  <si>
+    <t>sales_taxable_value</t>
+  </si>
+  <si>
+    <t>cash_back_taxable_value</t>
+  </si>
+  <si>
+    <t>total_invoice_value</t>
+  </si>
+  <si>
+    <t>total_taxable_value</t>
+  </si>
+  <si>
+    <t>aggregate_taxable_value</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(gstr1 report file b2cs worksheet) taxable value (state wise)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(GSTR Report file worksheet tcs_summary) Net Taxable Amount(state wise)</t>
+    </r>
+  </si>
+  <si>
+    <t>tcs_summary_net_taxable_amount</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1140,6 +1846,56 @@
     <font>
       <sz val="20"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF00B050"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF00B0F0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF0070C0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF7030A0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFC00000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1216,7 +1972,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1235,7 +1991,17 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1516,316 +2282,354 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B54"/>
+  <dimension ref="A1:R44"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="29.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="39.5703125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="29.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="26.25" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:18" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A1" s="6" t="s">
         <v>103</v>
       </c>
       <c r="B1" s="6" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="Q1" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="R1" s="8" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="Q2" s="8"/>
+      <c r="R2" s="8" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
         <v>126</v>
       </c>
       <c r="B3" s="7" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="Q3" s="8"/>
+      <c r="R3" s="8" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" s="7"/>
       <c r="B4" s="7" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="Q4" s="8"/>
+      <c r="R4" s="8" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5" s="7"/>
       <c r="B5" s="7" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="Q5" s="8"/>
+      <c r="R5" s="8" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6" s="7"/>
       <c r="B6" s="7" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="Q6" s="8"/>
+      <c r="R6" s="8" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7" s="7"/>
       <c r="B7" s="7" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="Q7" s="8"/>
+      <c r="R7" s="8" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A8" s="7"/>
       <c r="B8" s="7" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A9" s="7"/>
       <c r="B9" s="7" t="s">
         <v>125</v>
       </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="B11" s="8" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="8"/>
-      <c r="B12" s="8" t="s">
+      <c r="Q9" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="R9" s="9" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="Q10" s="9"/>
+      <c r="R10" s="9" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>156</v>
+      </c>
+      <c r="B11" t="s">
+        <v>157</v>
+      </c>
+      <c r="Q11" s="9"/>
+      <c r="R11" s="9" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="B12" t="s">
+        <v>158</v>
+      </c>
+      <c r="Q12" s="9"/>
+      <c r="R12" s="9" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="Q13" s="9"/>
+      <c r="R13" s="9" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="Q14" s="9"/>
+      <c r="R14" s="9" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="8"/>
-      <c r="B13" s="8" t="s">
+    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>159</v>
+      </c>
+      <c r="B15" t="s">
+        <v>164</v>
+      </c>
+      <c r="Q15" s="9"/>
+      <c r="R15" s="9" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="B16" t="s">
+        <v>165</v>
+      </c>
+      <c r="Q16" s="9"/>
+      <c r="R16" s="9" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="B17" t="s">
+        <v>166</v>
+      </c>
+      <c r="Q17" s="9"/>
+      <c r="R17" s="9" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="Q18" s="9"/>
+      <c r="R18" s="9" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="8"/>
-      <c r="B14" s="8" t="s">
+    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="Q19" s="9"/>
+      <c r="R19" s="9" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="8"/>
-      <c r="B15" s="8" t="s">
+    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>160</v>
+      </c>
+      <c r="B20" t="s">
+        <v>167</v>
+      </c>
+      <c r="Q20" s="9"/>
+      <c r="R20" s="9" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="8"/>
-      <c r="B16" s="8" t="s">
+    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="B21" t="s">
+        <v>168</v>
+      </c>
+      <c r="Q21" s="9"/>
+      <c r="R21" s="9" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="8"/>
-      <c r="B17" s="8" t="s">
+    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="Q23" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="R23" s="10" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>161</v>
+      </c>
+      <c r="B24" t="s">
+        <v>170</v>
+      </c>
+      <c r="Q24" s="10"/>
+      <c r="R24" s="10" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="B25" t="s">
+        <v>169</v>
+      </c>
+      <c r="Q25" s="10"/>
+      <c r="R25" s="10" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="Q26" s="10"/>
+      <c r="R26" s="10" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="Q27" s="10"/>
+      <c r="R27" s="10" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>162</v>
+      </c>
+      <c r="B28" t="s">
+        <v>173</v>
+      </c>
+      <c r="Q28" s="10"/>
+      <c r="R28" s="10" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="Q29" s="10"/>
+      <c r="R29" s="10" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="Q30" s="10"/>
+      <c r="R30" s="10" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="Q32" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="R32" s="11" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="33" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>163</v>
+      </c>
+      <c r="B33" t="s">
+        <v>171</v>
+      </c>
+      <c r="Q33" s="11"/>
+      <c r="R33" s="11" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="34" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="Q34" s="11"/>
+      <c r="R34" s="11" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="35" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="Q35" s="11"/>
+      <c r="R35" s="11" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="36" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="Q36" s="11"/>
+      <c r="R36" s="11" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="37" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="Q37" s="11"/>
+      <c r="R37" s="11" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="38" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="Q38" s="11"/>
+      <c r="R38" s="11" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="39" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="Q39" s="11"/>
+      <c r="R39" s="11" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="40" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="Q40" s="11"/>
+      <c r="R40" s="11" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="41" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="Q41" s="11"/>
+      <c r="R41" s="11" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="B19" s="9" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" s="9"/>
-      <c r="B20" s="9" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" s="9"/>
-      <c r="B21" s="9" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" s="9"/>
-      <c r="B22" s="9" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" s="9"/>
-      <c r="B23" s="9" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" s="9"/>
-      <c r="B24" s="9" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" s="9"/>
-      <c r="B25" s="9" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" s="9"/>
-      <c r="B26" s="9" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A27" s="9"/>
-      <c r="B27" s="9" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28" s="9"/>
-      <c r="B28" s="9" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29" s="9"/>
-      <c r="B29" s="9" t="s">
+    <row r="42" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="Q42" s="11"/>
+      <c r="R42" s="11" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A30" s="9"/>
-      <c r="B30" s="9" t="s">
+    <row r="43" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="Q43" s="11"/>
+      <c r="R43" s="11" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A31" s="9"/>
-      <c r="B31" s="9" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A33" s="10" t="s">
-        <v>60</v>
-      </c>
-      <c r="B33" s="10" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A34" s="10"/>
-      <c r="B34" s="10" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A35" s="10"/>
-      <c r="B35" s="10" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A36" s="10"/>
-      <c r="B36" s="10" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A37" s="10"/>
-      <c r="B37" s="10" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A38" s="10"/>
-      <c r="B38" s="10" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A39" s="10"/>
-      <c r="B39" s="10" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A40" s="10"/>
-      <c r="B40" s="10" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A42" s="11" t="s">
-        <v>53</v>
-      </c>
-      <c r="B42" s="11" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A43" s="11"/>
-      <c r="B43" s="11" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A44" s="11"/>
-      <c r="B44" s="11" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A45" s="11"/>
-      <c r="B45" s="11" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A46" s="11"/>
-      <c r="B46" s="11" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A47" s="11"/>
-      <c r="B47" s="11" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A48" s="11"/>
-      <c r="B48" s="11" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A49" s="11"/>
-      <c r="B49" s="11" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A50" s="11"/>
-      <c r="B50" s="11" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A51" s="11"/>
-      <c r="B51" s="11" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A52" s="11"/>
-      <c r="B52" s="11" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A53" s="11"/>
-      <c r="B53" s="11" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A54" s="11"/>
-      <c r="B54" s="11" t="s">
+    <row r="44" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="Q44" s="11"/>
+      <c r="R44" s="11" t="s">
         <v>23</v>
       </c>
     </row>
@@ -2335,140 +3139,365 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0230AE15-502F-4605-84EA-35E2D04EBBA1}">
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:D35"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="26.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="41.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.7109375" customWidth="1"/>
+    <col min="3" max="3" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="65.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" s="12" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="9" t="s">
         <v>109</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="9" t="s">
         <v>110</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
+      <c r="C2" s="9" t="s">
+        <v>130</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="57" x14ac:dyDescent="0.25">
+      <c r="A3" s="16" t="s">
         <v>106</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="13" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
+      <c r="C3" s="13"/>
+      <c r="D3" s="15" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="14" t="s">
         <v>107</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="13" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
+      <c r="C4" s="13"/>
+      <c r="D4" s="13"/>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="14" t="s">
         <v>108</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="13" t="s">
         <v>112</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C5" s="13"/>
+      <c r="D5" s="13"/>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="13"/>
+      <c r="B6" s="13"/>
+      <c r="C6" s="13"/>
+      <c r="D6" s="13"/>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="12" t="s">
         <v>113</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
+      <c r="B7" s="13"/>
+      <c r="C7" s="13"/>
+      <c r="D7" s="13"/>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="9" t="s">
         <v>109</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="9" t="s">
         <v>110</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="s">
+      <c r="C8" s="9" t="s">
+        <v>130</v>
+      </c>
+      <c r="D8" s="9" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="57" x14ac:dyDescent="0.25">
+      <c r="A9" s="14" t="s">
         <v>114</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="13" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
+      <c r="C9" s="13"/>
+      <c r="D9" s="15" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="14" t="s">
         <v>115</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="13" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="3" t="s">
+      <c r="C10" s="13"/>
+      <c r="D10" s="13"/>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="14" t="s">
         <v>116</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" s="13" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C11" s="13"/>
+      <c r="D11" s="13"/>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="13"/>
+      <c r="B12" s="13"/>
+      <c r="C12" s="13"/>
+      <c r="D12" s="13"/>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="s">
         <v>118</v>
       </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
+      <c r="B13" s="13"/>
+      <c r="C13" s="13"/>
+      <c r="D13" s="13"/>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="9" t="s">
         <v>109</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14" s="9" t="s">
         <v>110</v>
       </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" s="3" t="s">
+      <c r="C14" s="9" t="s">
+        <v>130</v>
+      </c>
+      <c r="D14" s="9" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="72" x14ac:dyDescent="0.25">
+      <c r="A15" s="14" t="s">
         <v>120</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15" s="15" t="s">
         <v>121</v>
       </c>
-      <c r="C15" t="s">
+      <c r="C15" s="13" t="s">
         <v>119</v>
       </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B16" t="s">
+      <c r="D15" s="15" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" s="13"/>
+      <c r="B16" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="C16" t="s">
+      <c r="C16" s="13" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
+      <c r="D16" s="13"/>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" s="13"/>
+      <c r="B17" s="13"/>
+      <c r="C17" s="13"/>
+      <c r="D17" s="13"/>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" s="12" t="s">
         <v>127</v>
       </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
+      <c r="B18" s="13"/>
+      <c r="C18" s="13"/>
+      <c r="D18" s="13"/>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" s="9" t="s">
         <v>109</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B19" s="9" t="s">
         <v>110</v>
       </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" s="3" t="s">
+      <c r="C19" s="9" t="s">
+        <v>130</v>
+      </c>
+      <c r="D19" s="9" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="36" x14ac:dyDescent="0.35">
+      <c r="A20" s="14" t="s">
         <v>128</v>
       </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" s="3" t="s">
+      <c r="B20" s="13" t="s">
+        <v>131</v>
+      </c>
+      <c r="C20" s="13"/>
+      <c r="D20" s="15" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" ht="36" x14ac:dyDescent="0.35">
+      <c r="A21" s="14"/>
+      <c r="B21" s="13" t="s">
+        <v>132</v>
+      </c>
+      <c r="C21" s="13"/>
+      <c r="D21" s="15" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" s="14"/>
+      <c r="B22" s="13" t="s">
+        <v>133</v>
+      </c>
+      <c r="C22" s="13"/>
+      <c r="D22" s="13"/>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" s="14"/>
+      <c r="B23" s="13"/>
+      <c r="C23" s="13"/>
+      <c r="D23" s="13"/>
+    </row>
+    <row r="24" spans="1:4" ht="36" x14ac:dyDescent="0.35">
+      <c r="A24" s="14" t="s">
         <v>129</v>
+      </c>
+      <c r="B24" s="13" t="s">
+        <v>134</v>
+      </c>
+      <c r="C24" s="13"/>
+      <c r="D24" s="15" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" ht="36" x14ac:dyDescent="0.35">
+      <c r="A25" s="13"/>
+      <c r="B25" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="C25" s="13"/>
+      <c r="D25" s="15" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26" s="13"/>
+      <c r="B26" s="13" t="s">
+        <v>136</v>
+      </c>
+      <c r="C26" s="13"/>
+      <c r="D26" s="13"/>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27" s="13"/>
+      <c r="B27" s="13" t="s">
+        <v>137</v>
+      </c>
+      <c r="C27" s="13"/>
+      <c r="D27" s="13"/>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28" s="13"/>
+      <c r="B28" s="13"/>
+      <c r="C28" s="13"/>
+      <c r="D28" s="13"/>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29" s="12" t="s">
+        <v>138</v>
+      </c>
+      <c r="B29" s="13"/>
+      <c r="C29" s="13"/>
+      <c r="D29" s="13"/>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="B30" s="9" t="s">
+        <v>110</v>
+      </c>
+      <c r="C30" s="9" t="s">
+        <v>130</v>
+      </c>
+      <c r="D30" s="9" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" ht="36" x14ac:dyDescent="0.25">
+      <c r="A31" s="14" t="s">
+        <v>139</v>
+      </c>
+      <c r="B31" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="C31" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="D31" s="15" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A32" s="13"/>
+      <c r="B32" s="13"/>
+      <c r="C32" s="13"/>
+      <c r="D32" s="13"/>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A33" s="12" t="s">
+        <v>142</v>
+      </c>
+      <c r="B33" s="13"/>
+      <c r="C33" s="13"/>
+      <c r="D33" s="13"/>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A34" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="B34" s="9" t="s">
+        <v>110</v>
+      </c>
+      <c r="C34" s="9" t="s">
+        <v>130</v>
+      </c>
+      <c r="D34" s="9" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" ht="51" x14ac:dyDescent="0.25">
+      <c r="A35" s="14" t="s">
+        <v>144</v>
+      </c>
+      <c r="B35" s="13" t="s">
+        <v>143</v>
+      </c>
+      <c r="C35" s="15" t="s">
+        <v>145</v>
+      </c>
+      <c r="D35" s="15" t="s">
+        <v>153</v>
       </c>
     </row>
   </sheetData>
